--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12300"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t>TestName</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>Radionica_Test_3</t>
+  </si>
+  <si>
+    <t>Invalid_MB_And_PIB</t>
+  </si>
+  <si>
+    <t>C12346</t>
   </si>
 </sst>
 </file>
@@ -700,7 +706,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1006,10 +1012,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="91.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1092,8 +1098,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F3" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>TestName</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>C12346</t>
+  </si>
+  <si>
+    <t>Vise_Vlasnika_Test</t>
+  </si>
+  <si>
+    <t>C12347</t>
   </si>
 </sst>
 </file>
@@ -1012,8 +1018,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
@@ -1118,8 +1124,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F5" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
   <si>
     <t>TestName</t>
   </si>
@@ -80,10 +80,16 @@
     <t>C12346</t>
   </si>
   <si>
-    <t>Vise_Vlasnika_Test</t>
+    <t>More_Owners</t>
   </si>
   <si>
     <t>C12347</t>
+  </si>
+  <si>
+    <t>Invalid_MB_And_PIB_Not_In_SBB</t>
+  </si>
+  <si>
+    <t>C12348</t>
   </si>
 </sst>
 </file>
@@ -1018,8 +1024,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
@@ -1144,8 +1150,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
   <si>
     <t>TestName</t>
   </si>
@@ -90,6 +90,24 @@
   </si>
   <si>
     <t>C12348</t>
+  </si>
+  <si>
+    <t>Withdraw_Request</t>
+  </si>
+  <si>
+    <t>C12349</t>
+  </si>
+  <si>
+    <t>Happy_path</t>
+  </si>
+  <si>
+    <t>C12350</t>
+  </si>
+  <si>
+    <t>Invalid_Email_And_Phone_Number</t>
+  </si>
+  <si>
+    <t>C12351</t>
   </si>
 </sst>
 </file>
@@ -1024,8 +1042,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
@@ -1170,8 +1188,68 @@
         <v>11</v>
       </c>
     </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F6" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F9" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
